--- a/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_BIELE ISB.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_BIELE ISB.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>T. SAGNA</t>
+          <t>M. OLAIZOLA GARIN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>51.1484</v>
+        <v>38.1733</v>
       </c>
       <c r="E2" t="n">
-        <v>40.8647</v>
+        <v>28.5883</v>
       </c>
       <c r="F2" t="n">
-        <v>10.2834</v>
+        <v>9.585000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>23.0123</v>
+        <v>21.724</v>
       </c>
       <c r="H2" t="n">
-        <v>16.2822</v>
+        <v>7.1044</v>
       </c>
       <c r="I2" t="n">
-        <v>6.7298</v>
+        <v>14.6195</v>
       </c>
       <c r="J2" t="n">
-        <v>40.1907</v>
+        <v>38.8572</v>
       </c>
       <c r="K2" t="n">
-        <v>30.6074</v>
+        <v>17.7597</v>
       </c>
       <c r="L2" t="n">
-        <v>9.5837</v>
+        <v>21.0978</v>
       </c>
       <c r="M2" t="n">
-        <v>-17.1782</v>
+        <v>-17.1334</v>
       </c>
       <c r="N2" t="n">
-        <v>-14.3251</v>
+        <v>-10.6555</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.8533</v>
+        <v>-6.478199999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>-12.4869</v>
+        <v>19.7714</v>
       </c>
       <c r="Q2" t="n">
-        <v>-44.7456</v>
+        <v>-17.2738</v>
       </c>
       <c r="R2" t="n">
-        <v>32.2582</v>
+        <v>37.0452</v>
       </c>
       <c r="S2" t="n">
-        <v>47.0089</v>
+        <v>9.308299999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>32.1705</v>
+        <v>2.9361</v>
       </c>
       <c r="U2" t="n">
-        <v>14.8389</v>
+        <v>6.3725</v>
       </c>
       <c r="V2" t="n">
-        <v>-6.385899999999999</v>
+        <v>-12.6306</v>
       </c>
       <c r="W2" t="n">
-        <v>13.2498</v>
+        <v>4.0687</v>
       </c>
       <c r="X2" t="n">
-        <v>-19.6359</v>
+        <v>-16.6992</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. OLAIZOLA GARIN</t>
+          <t>A. MONCANUT MORE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>33.5243</v>
+        <v>31.0521</v>
       </c>
       <c r="E3" t="n">
-        <v>23.2581</v>
+        <v>27.928</v>
       </c>
       <c r="F3" t="n">
-        <v>10.2664</v>
+        <v>3.124000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>21.724</v>
+        <v>16.626</v>
       </c>
       <c r="H3" t="n">
-        <v>7.1044</v>
+        <v>-1.7939</v>
       </c>
       <c r="I3" t="n">
-        <v>14.6195</v>
+        <v>18.4199</v>
       </c>
       <c r="J3" t="n">
-        <v>38.8572</v>
+        <v>51.3231</v>
       </c>
       <c r="K3" t="n">
-        <v>17.7597</v>
+        <v>24.1313</v>
       </c>
       <c r="L3" t="n">
-        <v>21.0978</v>
+        <v>27.1919</v>
       </c>
       <c r="M3" t="n">
-        <v>-17.1334</v>
+        <v>-34.6974</v>
       </c>
       <c r="N3" t="n">
-        <v>-10.6555</v>
+        <v>-25.9251</v>
       </c>
       <c r="O3" t="n">
-        <v>-6.478199999999999</v>
+        <v>-8.7721</v>
       </c>
       <c r="P3" t="n">
-        <v>19.7714</v>
+        <v>-4.5787</v>
       </c>
       <c r="Q3" t="n">
-        <v>-17.2738</v>
+        <v>-54.1109</v>
       </c>
       <c r="R3" t="n">
-        <v>37.0452</v>
+        <v>49.532</v>
       </c>
       <c r="S3" t="n">
-        <v>4.6597</v>
+        <v>11.6954</v>
       </c>
       <c r="T3" t="n">
-        <v>-2.394</v>
+        <v>4.4993</v>
       </c>
       <c r="U3" t="n">
-        <v>7.0537</v>
+        <v>7.1962</v>
       </c>
       <c r="V3" t="n">
-        <v>-12.6306</v>
+        <v>7.3095</v>
       </c>
       <c r="W3" t="n">
-        <v>4.0687</v>
+        <v>26.2163</v>
       </c>
       <c r="X3" t="n">
-        <v>-16.6992</v>
+        <v>-18.9067</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. MONCANUT MORE</t>
+          <t>I. AIZPITARTE ARANZA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D4" t="n">
-        <v>21.6513</v>
+        <v>26.5484</v>
       </c>
       <c r="E4" t="n">
-        <v>21.8433</v>
+        <v>18.8671</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1914999999999996</v>
+        <v>7.6812</v>
       </c>
       <c r="G4" t="n">
-        <v>16.626</v>
+        <v>11.6638</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.7939</v>
+        <v>-14.7253</v>
       </c>
       <c r="I4" t="n">
-        <v>18.4199</v>
+        <v>26.389</v>
       </c>
       <c r="J4" t="n">
-        <v>51.3231</v>
+        <v>32.8018</v>
       </c>
       <c r="K4" t="n">
-        <v>24.1313</v>
+        <v>1.3886</v>
       </c>
       <c r="L4" t="n">
-        <v>27.1919</v>
+        <v>31.4139</v>
       </c>
       <c r="M4" t="n">
-        <v>-34.6974</v>
+        <v>-21.1383</v>
       </c>
       <c r="N4" t="n">
-        <v>-25.9251</v>
+        <v>-16.1133</v>
       </c>
       <c r="O4" t="n">
-        <v>-8.7721</v>
+        <v>-5.0247</v>
       </c>
       <c r="P4" t="n">
-        <v>-4.5787</v>
+        <v>-8.9491</v>
       </c>
       <c r="Q4" t="n">
-        <v>-54.1109</v>
+        <v>-46.4104</v>
       </c>
       <c r="R4" t="n">
-        <v>49.532</v>
+        <v>37.4611</v>
       </c>
       <c r="S4" t="n">
-        <v>2.2945</v>
+        <v>6.9227</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.5857</v>
+        <v>1.4655</v>
       </c>
       <c r="U4" t="n">
-        <v>3.8806</v>
+        <v>5.457</v>
       </c>
       <c r="V4" t="n">
-        <v>7.3095</v>
+        <v>16.9117</v>
       </c>
       <c r="W4" t="n">
-        <v>26.2163</v>
+        <v>31.0103</v>
       </c>
       <c r="X4" t="n">
-        <v>-18.9067</v>
+        <v>-14.0988</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. JERMAIN</t>
+          <t>T. SAGNA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>16.4867</v>
+        <v>26.3309</v>
       </c>
       <c r="E5" t="n">
-        <v>13.0945</v>
+        <v>20.4122</v>
       </c>
       <c r="F5" t="n">
-        <v>3.392</v>
+        <v>5.9184</v>
       </c>
       <c r="G5" t="n">
-        <v>5.9478</v>
+        <v>23.0123</v>
       </c>
       <c r="H5" t="n">
-        <v>-4.3701</v>
+        <v>16.2822</v>
       </c>
       <c r="I5" t="n">
-        <v>10.318</v>
+        <v>6.7298</v>
       </c>
       <c r="J5" t="n">
-        <v>9.4681</v>
+        <v>40.1907</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.0416</v>
+        <v>30.6074</v>
       </c>
       <c r="L5" t="n">
-        <v>10.5096</v>
+        <v>9.5837</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.5202</v>
+        <v>-17.1782</v>
       </c>
       <c r="N5" t="n">
-        <v>-3.3284</v>
+        <v>-14.3251</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1917999999999999</v>
+        <v>-2.8533</v>
       </c>
       <c r="P5" t="n">
-        <v>1.4568</v>
+        <v>-12.4869</v>
       </c>
       <c r="Q5" t="n">
-        <v>-7.4923</v>
+        <v>-44.7456</v>
       </c>
       <c r="R5" t="n">
-        <v>8.9491</v>
+        <v>32.2582</v>
       </c>
       <c r="S5" t="n">
-        <v>-3.538</v>
+        <v>22.1916</v>
       </c>
       <c r="T5" t="n">
-        <v>-2.1662</v>
+        <v>11.7174</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.3717</v>
+        <v>10.4742</v>
       </c>
       <c r="V5" t="n">
-        <v>12.62</v>
+        <v>-6.385899999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>13.2851</v>
+        <v>13.2498</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6650999999999999</v>
+        <v>-19.6359</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. BADJI</t>
+          <t>J. JERMAIN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>16.1233</v>
+        <v>20.9145</v>
       </c>
       <c r="E6" t="n">
-        <v>12.0941</v>
+        <v>16.356</v>
       </c>
       <c r="F6" t="n">
-        <v>4.0293</v>
+        <v>4.5585</v>
       </c>
       <c r="G6" t="n">
-        <v>4.4269</v>
+        <v>5.9478</v>
       </c>
       <c r="H6" t="n">
-        <v>5.4613</v>
+        <v>-4.3701</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.0343</v>
+        <v>10.318</v>
       </c>
       <c r="J6" t="n">
-        <v>16.5166</v>
+        <v>9.4681</v>
       </c>
       <c r="K6" t="n">
-        <v>10.922</v>
+        <v>-1.0416</v>
       </c>
       <c r="L6" t="n">
-        <v>5.595</v>
+        <v>10.5096</v>
       </c>
       <c r="M6" t="n">
-        <v>-12.0898</v>
+        <v>-3.5202</v>
       </c>
       <c r="N6" t="n">
-        <v>-5.4605</v>
+        <v>-3.3284</v>
       </c>
       <c r="O6" t="n">
-        <v>-6.629</v>
+        <v>-0.1917999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.8731</v>
+        <v>1.4568</v>
       </c>
       <c r="Q6" t="n">
-        <v>-21.6444</v>
+        <v>-7.4923</v>
       </c>
       <c r="R6" t="n">
-        <v>19.7712</v>
+        <v>8.9491</v>
       </c>
       <c r="S6" t="n">
-        <v>21.1655</v>
+        <v>0.8899</v>
       </c>
       <c r="T6" t="n">
-        <v>11.4546</v>
+        <v>1.0951</v>
       </c>
       <c r="U6" t="n">
-        <v>9.710699999999999</v>
+        <v>-0.2051999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>-7.595899999999999</v>
+        <v>12.62</v>
       </c>
       <c r="W6" t="n">
-        <v>5.7668</v>
+        <v>13.2851</v>
       </c>
       <c r="X6" t="n">
-        <v>-13.3627</v>
+        <v>-0.6650999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. AIZPITARTE ARANZA</t>
+          <t>A. ACHA CORTABARRIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D7" t="n">
-        <v>12.1728</v>
+        <v>10.5409</v>
       </c>
       <c r="E7" t="n">
-        <v>8.8269</v>
+        <v>8.6257</v>
       </c>
       <c r="F7" t="n">
-        <v>3.3461</v>
+        <v>1.9153</v>
       </c>
       <c r="G7" t="n">
-        <v>11.6638</v>
+        <v>-16.4359</v>
       </c>
       <c r="H7" t="n">
-        <v>-14.7253</v>
+        <v>-12.8369</v>
       </c>
       <c r="I7" t="n">
-        <v>26.389</v>
+        <v>-3.599</v>
       </c>
       <c r="J7" t="n">
-        <v>32.8018</v>
+        <v>7.2828</v>
       </c>
       <c r="K7" t="n">
-        <v>1.3886</v>
+        <v>2.1951</v>
       </c>
       <c r="L7" t="n">
-        <v>31.4139</v>
+        <v>5.0876</v>
       </c>
       <c r="M7" t="n">
-        <v>-21.1383</v>
+        <v>-23.7184</v>
       </c>
       <c r="N7" t="n">
-        <v>-16.1133</v>
+        <v>-15.0319</v>
       </c>
       <c r="O7" t="n">
-        <v>-5.0247</v>
+        <v>-8.686400000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>-8.9491</v>
+        <v>14.9845</v>
       </c>
       <c r="Q7" t="n">
-        <v>-46.4104</v>
+        <v>-21.2281</v>
       </c>
       <c r="R7" t="n">
-        <v>37.4611</v>
+        <v>36.2126</v>
       </c>
       <c r="S7" t="n">
-        <v>-7.4532</v>
+        <v>10.0074</v>
       </c>
       <c r="T7" t="n">
-        <v>-8.5749</v>
+        <v>2.6345</v>
       </c>
       <c r="U7" t="n">
-        <v>1.1217</v>
+        <v>7.3728</v>
       </c>
       <c r="V7" t="n">
-        <v>16.9117</v>
+        <v>1.984700000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>31.0103</v>
+        <v>19.9365</v>
       </c>
       <c r="X7" t="n">
-        <v>-14.0988</v>
+        <v>-17.9516</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. ACHA CORTABARRIA</t>
+          <t>N. WILLIAMS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D8" t="n">
-        <v>8.779399999999999</v>
+        <v>8.898</v>
       </c>
       <c r="E8" t="n">
-        <v>8.2713</v>
+        <v>13.4473</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5078000000000005</v>
+        <v>-4.5495</v>
       </c>
       <c r="G8" t="n">
-        <v>-16.4359</v>
+        <v>14.3458</v>
       </c>
       <c r="H8" t="n">
-        <v>-12.8369</v>
+        <v>5.1892</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.599</v>
+        <v>9.1568</v>
       </c>
       <c r="J8" t="n">
-        <v>7.2828</v>
+        <v>32.1679</v>
       </c>
       <c r="K8" t="n">
-        <v>2.1951</v>
+        <v>14.1898</v>
       </c>
       <c r="L8" t="n">
-        <v>5.0876</v>
+        <v>17.978</v>
       </c>
       <c r="M8" t="n">
-        <v>-23.7184</v>
+        <v>-17.822</v>
       </c>
       <c r="N8" t="n">
-        <v>-15.0319</v>
+        <v>-9.0007</v>
       </c>
       <c r="O8" t="n">
-        <v>-8.686400000000001</v>
+        <v>-8.821300000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>14.9845</v>
+        <v>-8.3246</v>
       </c>
       <c r="Q8" t="n">
-        <v>-21.2281</v>
+        <v>-31.426</v>
       </c>
       <c r="R8" t="n">
-        <v>36.2126</v>
+        <v>23.1014</v>
       </c>
       <c r="S8" t="n">
-        <v>8.245699999999999</v>
+        <v>3.3827</v>
       </c>
       <c r="T8" t="n">
-        <v>2.2801</v>
+        <v>-2.6674</v>
       </c>
       <c r="U8" t="n">
-        <v>5.9654</v>
+        <v>6.0498</v>
       </c>
       <c r="V8" t="n">
-        <v>1.984700000000001</v>
+        <v>-0.5057999999999996</v>
       </c>
       <c r="W8" t="n">
-        <v>19.9365</v>
+        <v>15.3725</v>
       </c>
       <c r="X8" t="n">
-        <v>-17.9516</v>
+        <v>-15.8783</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. SAKHO</t>
+          <t>P. BADJI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>4.9485</v>
+        <v>5.2833</v>
       </c>
       <c r="E9" t="n">
-        <v>2.0109</v>
+        <v>4.2764</v>
       </c>
       <c r="F9" t="n">
-        <v>2.9376</v>
+        <v>1.0072</v>
       </c>
       <c r="G9" t="n">
-        <v>2.7037</v>
+        <v>4.4269</v>
       </c>
       <c r="H9" t="n">
-        <v>3.4671</v>
+        <v>5.4613</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7634000000000001</v>
+        <v>-1.0343</v>
       </c>
       <c r="J9" t="n">
-        <v>3.3</v>
+        <v>16.5166</v>
       </c>
       <c r="K9" t="n">
-        <v>3.8185</v>
+        <v>10.922</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5184</v>
+        <v>5.595</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5963000000000001</v>
+        <v>-12.0898</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3513000000000001</v>
+        <v>-5.4605</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2449</v>
+        <v>-6.629</v>
       </c>
       <c r="P9" t="n">
-        <v>1.2487</v>
+        <v>-1.8731</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.0812</v>
+        <v>-21.6444</v>
       </c>
       <c r="R9" t="n">
-        <v>3.3299</v>
+        <v>19.7712</v>
       </c>
       <c r="S9" t="n">
-        <v>2.8641</v>
+        <v>10.3256</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9158999999999998</v>
+        <v>3.6372</v>
       </c>
       <c r="U9" t="n">
-        <v>1.9482</v>
+        <v>6.6886</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.868</v>
+        <v>-7.595899999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.1238</v>
+        <v>5.7668</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.7442</v>
+        <v>-13.3627</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. KARRERA ALTUNA</t>
+          <t>M. SAKHO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>3.2216</v>
+        <v>3.6625</v>
       </c>
       <c r="E10" t="n">
-        <v>3.0134</v>
+        <v>1.6056</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2081</v>
+        <v>2.0568</v>
       </c>
       <c r="G10" t="n">
-        <v>2.5725</v>
+        <v>2.7037</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>3.4671</v>
       </c>
       <c r="I10" t="n">
-        <v>2.5725</v>
+        <v>-0.7634000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>2.4297</v>
+        <v>3.3</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>3.8185</v>
       </c>
       <c r="L10" t="n">
-        <v>2.4297</v>
+        <v>-0.5184</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1429</v>
+        <v>-0.5963000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>-0.3513000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1429</v>
+        <v>-0.2449</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.2487</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>3.3299</v>
       </c>
       <c r="S10" t="n">
-        <v>0.06519999999999999</v>
+        <v>1.578</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>0.5106000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>0.06519999999999999</v>
+        <v>1.0674</v>
       </c>
       <c r="V10" t="n">
-        <v>0.5838</v>
+        <v>-1.868</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5838</v>
+        <v>-0.1238</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.7442</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>U. BARANDALLA LUQUE</t>
+          <t>J. KARRERA ALTUNA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1.1096</v>
+        <v>3.2216</v>
       </c>
       <c r="E11" t="n">
-        <v>1.2677</v>
+        <v>3.0134</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1582</v>
+        <v>0.2081</v>
       </c>
       <c r="G11" t="n">
-        <v>4.1076</v>
+        <v>2.5725</v>
       </c>
       <c r="H11" t="n">
-        <v>2.2175</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1.89</v>
+        <v>2.5725</v>
       </c>
       <c r="J11" t="n">
-        <v>3.6627</v>
+        <v>2.4297</v>
       </c>
       <c r="K11" t="n">
-        <v>1.7033</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1.9594</v>
+        <v>2.4297</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4448</v>
+        <v>0.1429</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5142</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0694</v>
+        <v>0.1429</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.4568</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6244</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7274</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3138</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4136</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.8137</v>
+        <v>0.5838</v>
       </c>
       <c r="W11" t="n">
+        <v>0.5838</v>
+      </c>
+      <c r="X11" t="n">
         <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>-0.8137</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>N. WILLIAMS</t>
+          <t>O. INDA HERNANDEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4428999999999998</v>
+        <v>2.3991</v>
       </c>
       <c r="E12" t="n">
-        <v>7.031700000000001</v>
+        <v>-2.5893</v>
       </c>
       <c r="F12" t="n">
-        <v>-6.5889</v>
+        <v>4.9881</v>
       </c>
       <c r="G12" t="n">
-        <v>14.3458</v>
+        <v>6.021699999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>5.1892</v>
+        <v>8.4636</v>
       </c>
       <c r="I12" t="n">
-        <v>9.1568</v>
+        <v>-2.4419</v>
       </c>
       <c r="J12" t="n">
-        <v>32.1679</v>
+        <v>5.7371</v>
       </c>
       <c r="K12" t="n">
-        <v>14.1898</v>
+        <v>7.3463</v>
       </c>
       <c r="L12" t="n">
-        <v>17.978</v>
+        <v>-1.6091</v>
       </c>
       <c r="M12" t="n">
-        <v>-17.822</v>
+        <v>0.2847000000000003</v>
       </c>
       <c r="N12" t="n">
-        <v>-9.0007</v>
+        <v>1.1175</v>
       </c>
       <c r="O12" t="n">
-        <v>-8.821300000000001</v>
+        <v>-0.8327</v>
       </c>
       <c r="P12" t="n">
-        <v>-8.3246</v>
+        <v>-1.8729</v>
       </c>
       <c r="Q12" t="n">
-        <v>-31.426</v>
+        <v>-9.781599999999999</v>
       </c>
       <c r="R12" t="n">
-        <v>23.1014</v>
+        <v>7.9087</v>
       </c>
       <c r="S12" t="n">
-        <v>-5.0724</v>
+        <v>0.6207999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-9.082800000000001</v>
+        <v>0.2879</v>
       </c>
       <c r="U12" t="n">
-        <v>4.0105</v>
+        <v>0.333</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.5057999999999996</v>
+        <v>-2.3705</v>
       </c>
       <c r="W12" t="n">
-        <v>15.3725</v>
+        <v>1.1675</v>
       </c>
       <c r="X12" t="n">
-        <v>-15.8783</v>
+        <v>-3.538</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>O. INDA HERNANDEZ</t>
+          <t>U. BARANDALLA LUQUE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,70 +1420,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.08530000000000015</v>
+        <v>1.3929</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.934</v>
+        <v>1.3749</v>
       </c>
       <c r="F13" t="n">
-        <v>3.0192</v>
+        <v>0.018</v>
       </c>
       <c r="G13" t="n">
-        <v>6.021699999999999</v>
+        <v>4.1076</v>
       </c>
       <c r="H13" t="n">
-        <v>8.4636</v>
+        <v>2.2175</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.4419</v>
+        <v>1.89</v>
       </c>
       <c r="J13" t="n">
-        <v>5.7371</v>
+        <v>3.6627</v>
       </c>
       <c r="K13" t="n">
-        <v>7.3463</v>
+        <v>1.7033</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.6091</v>
+        <v>1.9594</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2847000000000003</v>
+        <v>0.4448</v>
       </c>
       <c r="N13" t="n">
-        <v>1.1175</v>
+        <v>0.5142</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.8327</v>
+        <v>-0.0694</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.8729</v>
+        <v>-1.4568</v>
       </c>
       <c r="Q13" t="n">
-        <v>-9.781599999999999</v>
+        <v>-2.0812</v>
       </c>
       <c r="R13" t="n">
-        <v>7.9087</v>
+        <v>0.6244</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.693</v>
+        <v>-0.4441</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0568999999999999</v>
+        <v>-0.2067</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.636</v>
+        <v>-0.2374</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.3705</v>
+        <v>-0.8137</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.538</v>
+        <v>-0.8137</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>15</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.1111</v>
+        <v>-2.3497</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.3349</v>
+        <v>-1.9184</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.776</v>
+        <v>-0.4313999999999996</v>
       </c>
       <c r="G14" t="n">
         <v>-3.8518</v>
@@ -1546,13 +1546,13 @@
         <v>12.9032</v>
       </c>
       <c r="S14" t="n">
-        <v>-5.0899</v>
+        <v>-1.3291</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.6577</v>
+        <v>-2.2413</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.4325</v>
+        <v>0.9123000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-1.5392</v>
@@ -1579,13 +1579,13 @@
         <v>22</v>
       </c>
       <c r="D15" t="n">
-        <v>-6.8224</v>
+        <v>-4.0662</v>
       </c>
       <c r="E15" t="n">
-        <v>-6.8333</v>
+        <v>-4.662100000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0112000000000001</v>
+        <v>0.5962000000000001</v>
       </c>
       <c r="G15" t="n">
         <v>-19.3593</v>
@@ -1624,13 +1624,13 @@
         <v>26.223</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8675999999999999</v>
+        <v>3.6242</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1067</v>
+        <v>2.0646</v>
       </c>
       <c r="U15" t="n">
-        <v>0.974</v>
+        <v>1.5594</v>
       </c>
       <c r="V15" t="n">
         <v>7.2987</v>
@@ -1657,13 +1657,13 @@
         <v>25</v>
       </c>
       <c r="D16" t="n">
-        <v>-14.5248</v>
+        <v>-7.316</v>
       </c>
       <c r="E16" t="n">
-        <v>-6.522</v>
+        <v>-0.8752000000000013</v>
       </c>
       <c r="F16" t="n">
-        <v>-8.002800000000001</v>
+        <v>-6.4411</v>
       </c>
       <c r="G16" t="n">
         <v>-0.9227000000000001</v>
@@ -1702,13 +1702,13 @@
         <v>20.1874</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.6363</v>
+        <v>4.5724</v>
       </c>
       <c r="T16" t="n">
-        <v>-2.764</v>
+        <v>2.8825</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1277000000000001</v>
+        <v>1.6895</v>
       </c>
       <c r="V16" t="n">
         <v>-11.5904</v>
@@ -1735,13 +1735,13 @@
         <v>26</v>
       </c>
       <c r="D17" t="n">
-        <v>-16.9814</v>
+        <v>-18.8049</v>
       </c>
       <c r="E17" t="n">
-        <v>-6.658199999999998</v>
+        <v>-10.6738</v>
       </c>
       <c r="F17" t="n">
-        <v>-10.3234</v>
+        <v>-8.1313</v>
       </c>
       <c r="G17" t="n">
         <v>-20.9882</v>
@@ -1780,13 +1780,13 @@
         <v>44.5375</v>
       </c>
       <c r="S17" t="n">
-        <v>14.7338</v>
+        <v>12.9098</v>
       </c>
       <c r="T17" t="n">
-        <v>9.3726</v>
+        <v>5.357</v>
       </c>
       <c r="U17" t="n">
-        <v>5.361</v>
+        <v>7.5528</v>
       </c>
       <c r="V17" t="n">
         <v>-3.4427</v>
@@ -1813,19 +1813,19 @@
         <v>26</v>
       </c>
       <c r="D18" t="n">
-        <v>125.2544</v>
+        <v>145.8807</v>
       </c>
       <c r="E18" t="n">
-        <v>115.2942</v>
+        <v>123.7761</v>
       </c>
       <c r="F18" t="n">
-        <v>9.960299999999998</v>
+        <v>22.1035</v>
       </c>
       <c r="G18" t="n">
-        <v>51.59419999999999</v>
+        <v>51.5942</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.350899999999996</v>
+        <v>-2.350899999999999</v>
       </c>
       <c r="I18" t="n">
         <v>53.94449999999999</v>
@@ -1849,7 +1849,7 @@
         <v>-71.0462</v>
       </c>
       <c r="P18" t="n">
-        <v>0.0006999999999992568</v>
+        <v>0.000700000000005474</v>
       </c>
       <c r="Q18" t="n">
         <v>-360.0457</v>
@@ -1858,16 +1858,16 @@
         <v>360.0449</v>
       </c>
       <c r="S18" t="n">
-        <v>75.69479999999999</v>
+        <v>96.32079999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>25.49100000000001</v>
+        <v>33.9723</v>
       </c>
       <c r="U18" t="n">
-        <v>50.2038</v>
+        <v>62.3481</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.034300000000002</v>
+        <v>-2.034299999999997</v>
       </c>
       <c r="W18" t="n">
         <v>182.5236</v>
